--- a/output/yearly_surface_area_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_41_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497642258177</v>
+        <v>10.84497639904186</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907225679023</v>
+        <v>37.78907217476596</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39274013942773</v>
+        <v>4.861614631430205</v>
       </c>
       <c r="C2" t="n">
-        <v>14.74094177926586</v>
+        <v>16.77512302246525</v>
       </c>
       <c r="D2" t="n">
-        <v>27.42708561354314</v>
+        <v>31.10765775676444</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.28228567493335</v>
+        <v>15.06000978314607</v>
       </c>
       <c r="C3" t="n">
-        <v>32.45657910239955</v>
+        <v>33.0259927708627</v>
       </c>
       <c r="D3" t="n">
-        <v>56.56339398017998</v>
+        <v>65.17332134642452</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.50588747179015</v>
+        <v>34.30619177720055</v>
       </c>
       <c r="C4" t="n">
-        <v>64.78356750783853</v>
+        <v>84.82103815151592</v>
       </c>
       <c r="D4" t="n">
-        <v>57.38118981781757</v>
+        <v>75.42767611728245</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.48575379608648</v>
+        <v>41.42975311921541</v>
       </c>
       <c r="C5" t="n">
-        <v>102.8871594050658</v>
+        <v>144.8323300690107</v>
       </c>
       <c r="D5" t="n">
-        <v>42.65693774952392</v>
+        <v>57.67767762450012</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.06927178530758</v>
+        <v>37.07177506006381</v>
       </c>
       <c r="C6" t="n">
-        <v>140.9612988711656</v>
+        <v>173.6858950968245</v>
       </c>
       <c r="D6" t="n">
-        <v>36.91076843656734</v>
+        <v>44.39757642915352</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.06307819944583</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>140.2544405241078</v>
+        <v>157.2622377524796</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.68832831386403</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>100.1382658331747</v>
+        <v>94.88100687693299</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>53.13905798776709</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.685097893264078</v>
+        <v>7.657341948503965</v>
       </c>
       <c r="C21" t="n">
-        <v>93.18181195582694</v>
+        <v>92.84527112561058</v>
       </c>
       <c r="D21" t="n">
-        <v>8.645735129922087</v>
+        <v>7.657341948503965</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.262568605390403</v>
+        <v>6.427502219703868</v>
       </c>
       <c r="C2" t="n">
-        <v>10.53218937115978</v>
+        <v>10.63429113240145</v>
       </c>
       <c r="D2" t="n">
-        <v>29.38763577892402</v>
+        <v>36.12340677776139</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02841393016093</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="C3" t="n">
-        <v>45.05731088640736</v>
+        <v>48.33634821859171</v>
       </c>
       <c r="D3" t="n">
-        <v>63.715426005618</v>
+        <v>72.46279805045707</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.92781800043802</v>
+        <v>31.12827445855362</v>
       </c>
       <c r="C4" t="n">
-        <v>72.8368439257751</v>
+        <v>82.7024266057513</v>
       </c>
       <c r="D4" t="n">
-        <v>70.2715371745782</v>
+        <v>86.85031065619407</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.45554060143309</v>
+        <v>45.45491870662732</v>
       </c>
       <c r="C5" t="n">
-        <v>109.7348496421873</v>
+        <v>149.8883307458818</v>
       </c>
       <c r="D5" t="n">
-        <v>51.3454049321082</v>
+        <v>69.335931612431</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.5284109157256</v>
+        <v>45.12210623488766</v>
       </c>
       <c r="C6" t="n">
-        <v>152.1110075482966</v>
+        <v>197.3136170949325</v>
       </c>
       <c r="D6" t="n">
-        <v>41.45920555034281</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.64493579289469</v>
+        <v>33.59638818703009</v>
       </c>
       <c r="C7" t="n">
-        <v>169.4192195741678</v>
+        <v>198.2246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.28214680621311</v>
+        <v>19.02627050830318</v>
       </c>
       <c r="C8" t="n">
-        <v>141.1115062699153</v>
+        <v>145.9515224518521</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>85.42186774651495</v>
+        <v>77.54530591534278</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.86429464716567</v>
+        <v>7.826199866523052</v>
       </c>
       <c r="C21" t="n">
-        <v>101.252793582258</v>
+        <v>100.7623232814843</v>
       </c>
       <c r="D21" t="n">
-        <v>9.830368308957086</v>
+        <v>8.804474849838433</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.672358308688823</v>
+        <v>6.341108421730148</v>
       </c>
       <c r="C2" t="n">
-        <v>16.51299638543135</v>
+        <v>8.225082266179777</v>
       </c>
       <c r="D2" t="n">
-        <v>23.8378160068168</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.51085296357361</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>42.74529504290612</v>
+        <v>44.73824288252715</v>
       </c>
       <c r="D3" t="n">
-        <v>69.62063844666255</v>
+        <v>81.49487692952773</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.27691927252238</v>
+        <v>29.44359539806609</v>
       </c>
       <c r="C4" t="n">
-        <v>89.76021085158163</v>
+        <v>98.71964040053801</v>
       </c>
       <c r="D4" t="n">
-        <v>81.1964256274367</v>
+        <v>97.02219861989529</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.1119289049467</v>
+        <v>45.4794623992335</v>
       </c>
       <c r="C5" t="n">
-        <v>120.2640937702343</v>
+        <v>148.9311267342412</v>
       </c>
       <c r="D5" t="n">
-        <v>61.85010536754907</v>
+        <v>79.66882619962867</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.24414604985053</v>
+        <v>51.07935130425731</v>
       </c>
       <c r="C6" t="n">
-        <v>160.4833519701134</v>
+        <v>212.3274847359789</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>58.40515267334701</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.0471335564664</v>
+        <v>41.26187426178919</v>
       </c>
       <c r="C7" t="n">
-        <v>190.4993062797553</v>
+        <v>234.5758512096201</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>45.63359678880023</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="C8" t="n">
-        <v>178.2461131830509</v>
+        <v>191.6813305156685</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.41874860582365</v>
+        <v>13.31249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>122.5859270907779</v>
+        <v>117.8156149958427</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>69.18376071827274</v>
+        <v>61.4966761940202</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>42.29172760354408</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.026823478405676</v>
+        <v>7.97744755784661</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3654698932773</v>
+        <v>107.6955420309292</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0368822828078</v>
+        <v>9.971809447308262</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.966481709335367</v>
+        <v>5.915029918087032</v>
       </c>
       <c r="C2" t="n">
-        <v>11.36078443354409</v>
+        <v>5.790347959647687</v>
       </c>
       <c r="D2" t="n">
-        <v>19.73803759388212</v>
+        <v>28.9173786285898</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.24640297823272</v>
+        <v>20.40071729424872</v>
       </c>
       <c r="C3" t="n">
-        <v>64.53027660014286</v>
+        <v>63.66142988188442</v>
       </c>
       <c r="D3" t="n">
-        <v>73.08620784265381</v>
+        <v>85.35805414573893</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.58550684682537</v>
+        <v>21.84977690571701</v>
       </c>
       <c r="C4" t="n">
-        <v>109.1467827673434</v>
+        <v>125.5213527264759</v>
       </c>
       <c r="D4" t="n">
-        <v>75.22347259479911</v>
+        <v>91.43212719191393</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.81491701444964</v>
+        <v>28.76520773443155</v>
       </c>
       <c r="C5" t="n">
-        <v>95.89220701230721</v>
+        <v>126.8663470812941</v>
       </c>
       <c r="D5" t="n">
-        <v>44.25227776892498</v>
+        <v>55.54237636776331</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.43025184083414</v>
+        <v>25.60005313593983</v>
       </c>
       <c r="C6" t="n">
-        <v>125.4644113596297</v>
+        <v>154.4858552448696</v>
       </c>
       <c r="D6" t="n">
-        <v>27.45162930614931</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>125.342674644303</v>
+        <v>134.8047590178338</v>
       </c>
       <c r="D7" t="n">
-        <v>27.48795397120644</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>90.29133635957915</v>
+        <v>86.78649705541802</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>46.92655851529327</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.245077073163208</v>
+        <v>3.621667280966483</v>
       </c>
       <c r="C2" t="n">
-        <v>5.302419350637023</v>
+        <v>2.997275741065512</v>
       </c>
       <c r="D2" t="n">
-        <v>15.06786376478004</v>
+        <v>21.24502031990098</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6552109338269</v>
+        <v>20.80814259151115</v>
       </c>
       <c r="C3" t="n">
-        <v>55.38529673508381</v>
+        <v>44.35045253934966</v>
       </c>
       <c r="D3" t="n">
-        <v>73.0567554115264</v>
+        <v>88.15603510284234</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.81746134693488</v>
+        <v>28.79269667015045</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0798693592012</v>
+        <v>145.3929080081356</v>
       </c>
       <c r="D4" t="n">
-        <v>90.18138061670351</v>
+        <v>109.1978336479642</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.03014074585795</v>
+        <v>31.6122760767473</v>
       </c>
       <c r="C5" t="n">
-        <v>144.4641746799182</v>
+        <v>173.0575765661065</v>
       </c>
       <c r="D5" t="n">
-        <v>56.27868714594842</v>
+        <v>68.77142668248908</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>30.22899356146354</v>
       </c>
       <c r="C6" t="n">
-        <v>142.5713651061303</v>
+        <v>181.4544646805295</v>
       </c>
       <c r="D6" t="n">
-        <v>32.24157635516951</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>152.5311955657142</v>
+        <v>168.580807034741</v>
       </c>
       <c r="D7" t="n">
-        <v>30.06307819944583</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>116.3272854762046</v>
+        <v>114.9086600435679</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>49.92187076095029</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.219551632852791</v>
+        <v>4.224460371374025</v>
       </c>
       <c r="C2" t="n">
-        <v>5.018694264109694</v>
+        <v>4.824308218668826</v>
       </c>
       <c r="D2" t="n">
-        <v>12.66356363707961</v>
+        <v>17.81086685044563</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.02136176978195</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="C3" t="n">
-        <v>37.39967879328224</v>
+        <v>27.58711048933537</v>
       </c>
       <c r="D3" t="n">
-        <v>68.45726741713008</v>
+        <v>85.53476873250335</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.2881604656256</v>
+        <v>33.42556408649115</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0415811987355</v>
+        <v>129.6054231761427</v>
       </c>
       <c r="D4" t="n">
-        <v>103.7098639812246</v>
+        <v>124.3088943117311</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>36.71736413883072</v>
       </c>
       <c r="C5" t="n">
-        <v>197.2331137831843</v>
+        <v>216.4999124790279</v>
       </c>
       <c r="D5" t="n">
-        <v>72.5511553438393</v>
+        <v>86.34471058850698</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>35.54221213684728</v>
       </c>
       <c r="C6" t="n">
-        <v>184.2318289358437</v>
+        <v>222.9941735426206</v>
       </c>
       <c r="D6" t="n">
-        <v>40.45291415348983</v>
+        <v>46.41015922285948</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.80545939030566</v>
+        <v>23.47555110394973</v>
       </c>
       <c r="C7" t="n">
-        <v>177.5637985285993</v>
+        <v>211.8788260351381</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>156.0487975900305</v>
+        <v>161.806747875438</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>28.70630287217673</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>95.29530440812512</v>
+        <v>86.64218014289374</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.541744806294992</v>
+        <v>2.537817815478005</v>
       </c>
       <c r="C2" t="n">
-        <v>2.408227118517426</v>
+        <v>2.397427893770711</v>
       </c>
       <c r="D2" t="n">
-        <v>8.85241904919349</v>
+        <v>12.61251275645877</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.82501222893259</v>
+        <v>17.15113239319178</v>
       </c>
       <c r="C3" t="n">
-        <v>32.28477325415636</v>
+        <v>25.79542092908494</v>
       </c>
       <c r="D3" t="n">
-        <v>66.38577976116932</v>
+        <v>84.09159960726055</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.27012915405066</v>
+        <v>36.39927788265474</v>
       </c>
       <c r="C4" t="n">
-        <v>135.4890371676938</v>
+        <v>122.1264691651905</v>
       </c>
       <c r="D4" t="n">
-        <v>112.3119373658351</v>
+        <v>134.889189320399</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.63868545377073</v>
+        <v>38.06726723217008</v>
       </c>
       <c r="C5" t="n">
-        <v>241.8780906338079</v>
+        <v>257.7087723647878</v>
       </c>
       <c r="D5" t="n">
-        <v>77.3371754020425</v>
+        <v>89.14269154561039</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>28.33716573537994</v>
       </c>
       <c r="C6" t="n">
-        <v>220.6998291577958</v>
+        <v>260.1062002585585</v>
       </c>
       <c r="D6" t="n">
-        <v>40.57366912111219</v>
+        <v>45.56487444950297</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.982991493858314</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>193.37386355779</v>
+        <v>215.7115690725177</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>116.0769398116216</v>
+        <v>109.8182981970482</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.403719290623691</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="C2" t="n">
-        <v>5.588107932572845</v>
+        <v>10.87383757223767</v>
       </c>
       <c r="D2" t="n">
-        <v>10.71773968726243</v>
+        <v>14.59564311903733</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.00953973960199</v>
+        <v>13.16032797542849</v>
       </c>
       <c r="C3" t="n">
-        <v>20.83268628411732</v>
+        <v>17.72545480017616</v>
       </c>
       <c r="D3" t="n">
-        <v>59.55281573961152</v>
+        <v>75.87928006123597</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.24536447726624</v>
+        <v>34.52315801983909</v>
       </c>
       <c r="C4" t="n">
-        <v>108.9170538045496</v>
+        <v>95.91184196639215</v>
       </c>
       <c r="D4" t="n">
-        <v>118.1572631969206</v>
+        <v>143.6444153468721</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.05717201768713</v>
+        <v>44.89041377668541</v>
       </c>
       <c r="C5" t="n">
-        <v>247.4004214701963</v>
+        <v>242.6880324898116</v>
       </c>
       <c r="D5" t="n">
-        <v>94.93500300066657</v>
+        <v>111.7965198211056</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>36.91076843656734</v>
       </c>
       <c r="C6" t="n">
-        <v>293.5150746340775</v>
+        <v>328.4132602769388</v>
       </c>
       <c r="D6" t="n">
-        <v>51.60262283062086</v>
+        <v>57.51961624411638</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>249.9667099690974</v>
+        <v>281.4670668075605</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>172.4047143427823</v>
+        <v>177.3281790795801</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>74.66093116026566</v>
+        <v>68.22655670663207</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.56913593102267</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.34962535589888</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.401354884587698</v>
+        <v>1.758310138306037</v>
       </c>
       <c r="C2" t="n">
-        <v>3.190680038802134</v>
+        <v>6.510950774564847</v>
       </c>
       <c r="D2" t="n">
-        <v>8.460701715199011</v>
+        <v>10.79235251278519</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.10142311317368</v>
+        <v>11.35391219961436</v>
       </c>
       <c r="C3" t="n">
-        <v>21.63281066307847</v>
+        <v>28.47559216167874</v>
       </c>
       <c r="D3" t="n">
-        <v>56.16578615996002</v>
+        <v>71.5448639469863</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.07195498651306</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>88.22868443295661</v>
+        <v>77.53352494289186</v>
       </c>
       <c r="D4" t="n">
-        <v>120.2758747426852</v>
+        <v>147.3456041918825</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.47503668679778</v>
+        <v>48.22835597112457</v>
       </c>
       <c r="C5" t="n">
-        <v>236.257585026995</v>
+        <v>227.3727683035613</v>
       </c>
       <c r="D5" t="n">
-        <v>107.820441618906</v>
+        <v>127.8971821707532</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.20010627187966</v>
+        <v>42.50574860306991</v>
       </c>
       <c r="C6" t="n">
-        <v>339.3214590188251</v>
+        <v>361.8221346524578</v>
       </c>
       <c r="D6" t="n">
-        <v>59.97496725243766</v>
+        <v>67.62278186852032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>13.41460063082842</v>
       </c>
       <c r="C7" t="n">
-        <v>310.9312789074158</v>
+        <v>342.5514089657971</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>216.6324484191012</v>
+        <v>227.5642091058894</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>83.53593040665682</v>
+        <v>72.33124385808797</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.623630776374977</v>
+        <v>2.778346003018473</v>
       </c>
       <c r="C2" t="n">
-        <v>12.01659189998096</v>
+        <v>7.363107781851078</v>
       </c>
       <c r="D2" t="n">
-        <v>12.43776166510284</v>
+        <v>11.66316272645211</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.7108674533327</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C3" t="n">
-        <v>17.32293824143497</v>
+        <v>27.06678420608456</v>
       </c>
       <c r="D3" t="n">
-        <v>51.44357970253287</v>
+        <v>65.10950774564847</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.46461301048277</v>
+        <v>27.17183121043897</v>
       </c>
       <c r="C4" t="n">
-        <v>73.18143736996574</v>
+        <v>73.79404793741575</v>
       </c>
       <c r="D4" t="n">
-        <v>118.9230264062331</v>
+        <v>148.0603165205742</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.90424036000288</v>
+        <v>47.71293842639499</v>
       </c>
       <c r="C5" t="n">
-        <v>205.1116391097649</v>
+        <v>192.5698121880119</v>
       </c>
       <c r="D5" t="n">
-        <v>121.1231230114503</v>
+        <v>143.4087958978529</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.17622553180826</v>
+        <v>50.2340665309008</v>
       </c>
       <c r="C6" t="n">
-        <v>354.5365849392422</v>
+        <v>362.9491810169332</v>
       </c>
       <c r="D6" t="n">
-        <v>73.78128521726055</v>
+        <v>82.47564288607032</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.84160412891355</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>381.1183857794288</v>
+        <v>414.8345471863769</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>292.9044275620358</v>
+        <v>308.175513101595</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>148.4343623958922</v>
+        <v>142.8874878668977</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.78053048260522</v>
+        <v>4.932300466135975</v>
       </c>
       <c r="C2" t="n">
-        <v>11.67494369890307</v>
+        <v>9.642725951112171</v>
       </c>
       <c r="D2" t="n">
-        <v>4.077198215737003</v>
+        <v>11.40005434171396</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.61930287493049</v>
+        <v>2.050870954171587</v>
       </c>
       <c r="C2" t="n">
-        <v>7.0175325899562</v>
+        <v>4.358959806855839</v>
       </c>
       <c r="D2" t="n">
-        <v>9.252972112526189</v>
+        <v>8.67668621013331</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.46605242207675</v>
+        <v>11.98223073033232</v>
       </c>
       <c r="C3" t="n">
-        <v>28.10743677258618</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D3" t="n">
-        <v>55.93998418798326</v>
+        <v>70.14096472991336</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.68304402691108</v>
+        <v>36.57795596482766</v>
       </c>
       <c r="C4" t="n">
-        <v>108.9553419650153</v>
+        <v>108.4703585991173</v>
       </c>
       <c r="D4" t="n">
-        <v>121.2841296349467</v>
+        <v>149.3748766965607</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.90113088597411</v>
+        <v>28.74066404182538</v>
       </c>
       <c r="C5" t="n">
-        <v>303.6791086161447</v>
+        <v>300.1693605734623</v>
       </c>
       <c r="D5" t="n">
-        <v>109.6857622569749</v>
+        <v>126.9890655443249</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.11953654020664</v>
+        <v>15.33588088803943</v>
       </c>
       <c r="C6" t="n">
-        <v>313.5603992593889</v>
+        <v>333.6862271964484</v>
       </c>
       <c r="D6" t="n">
-        <v>61.14226527278711</v>
+        <v>67.34102027740147</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>205.9500516491916</v>
+        <v>216.7296414418216</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>109.4010554227433</v>
+        <v>105.3120762345553</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.748533718992575</v>
+        <v>5.893431468593603</v>
       </c>
       <c r="C2" t="n">
-        <v>6.523713494720055</v>
+        <v>8.980046250745575</v>
       </c>
       <c r="D2" t="n">
-        <v>7.10098114481718</v>
+        <v>13.50884841043611</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.2816637801276</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C3" t="n">
-        <v>29.41806995775567</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="D3" t="n">
-        <v>6.562983402889927</v>
+        <v>12.7136327699962</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39830541589785</v>
+        <v>13.3975429874824</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14406953028875</v>
+        <v>70.14007799329019</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576271225399747</v>
+        <v>1.576181527939105</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.908738521234052</v>
+        <v>4.277474747403353</v>
       </c>
       <c r="C2" t="n">
-        <v>6.547275439621979</v>
+        <v>9.780170629706724</v>
       </c>
       <c r="D2" t="n">
-        <v>9.738937226128359</v>
+        <v>18.05237678569035</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.89373456822987</v>
+        <v>16.39518666092173</v>
       </c>
       <c r="C3" t="n">
-        <v>26.92933952749001</v>
+        <v>31.00850123863551</v>
       </c>
       <c r="D3" t="n">
-        <v>10.9415781638307</v>
+        <v>20.98485717827557</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.29424657383356</v>
+        <v>12.27773678931061</v>
       </c>
       <c r="C4" t="n">
-        <v>45.34594471145593</v>
+        <v>37.57344813693393</v>
       </c>
       <c r="D4" t="n">
-        <v>18.50594422505237</v>
+        <v>21.73491242432013</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44149178312468</v>
+        <v>15.43928530579344</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14726994795878</v>
+        <v>86.13496012705814</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250840375394671</v>
+        <v>3.25037585385125</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.769731257858504</v>
+        <v>5.393721887131976</v>
       </c>
       <c r="C2" t="n">
-        <v>7.685121028844032</v>
+        <v>11.6337102953247</v>
       </c>
       <c r="D2" t="n">
-        <v>12.54575391256999</v>
+        <v>15.69912753861074</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>15.50670498857837</v>
       </c>
       <c r="C3" t="n">
-        <v>26.05067533218912</v>
+        <v>35.58344554042564</v>
       </c>
       <c r="D3" t="n">
-        <v>16.19392838155114</v>
+        <v>30.55689729468197</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.95486496780043</v>
+        <v>23.3302524437212</v>
       </c>
       <c r="C4" t="n">
-        <v>58.36391926976863</v>
+        <v>60.39319177444678</v>
       </c>
       <c r="D4" t="n">
-        <v>19.84602984134927</v>
+        <v>27.37603473292231</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.51728322914684</v>
+        <v>10.97103059495811</v>
       </c>
       <c r="C5" t="n">
-        <v>50.04458922398117</v>
+        <v>41.8469958935203</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>30.48326621686347</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73481469774962</v>
+        <v>16.72943174131654</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0823696562727</v>
+        <v>102.0495336220309</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020444409324887</v>
+        <v>4.182357935329136</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.42317431825938</v>
+        <v>4.928373475318988</v>
       </c>
       <c r="C2" t="n">
-        <v>5.652903281053134</v>
+        <v>6.335217935504667</v>
       </c>
       <c r="D2" t="n">
-        <v>18.07692047829652</v>
+        <v>16.00543282233575</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.89373456822987</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C3" t="n">
-        <v>28.21542902005333</v>
+        <v>40.96342295969816</v>
       </c>
       <c r="D3" t="n">
-        <v>22.12368451520187</v>
+        <v>35.69143778789279</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.19208805932966</v>
+        <v>26.72513600500667</v>
       </c>
       <c r="C4" t="n">
-        <v>62.17997259617598</v>
+        <v>75.51701515836891</v>
       </c>
       <c r="D4" t="n">
-        <v>23.29196428325558</v>
+        <v>36.02915899815369</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.33538216642069</v>
+        <v>22.97289627937537</v>
       </c>
       <c r="C5" t="n">
-        <v>80.74874867430016</v>
+        <v>79.47247665877931</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>33.08489763311751</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>47.53720558733482</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05934909217491</v>
+        <v>18.04863349128367</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8157536013315</v>
+        <v>117.745847062184</v>
       </c>
       <c r="D21" t="n">
-        <v>6.87975203511425</v>
+        <v>6.016211163761224</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.530585728649783</v>
+        <v>6.712209053935443</v>
       </c>
       <c r="C2" t="n">
-        <v>5.773658248675491</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D2" t="n">
-        <v>18.65615162380214</v>
+        <v>26.41195848735194</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.65044106402591</v>
+        <v>15.01583113645496</v>
       </c>
       <c r="C3" t="n">
-        <v>23.13488465057609</v>
+        <v>29.76659039276329</v>
       </c>
       <c r="D3" t="n">
-        <v>29.1039106923967</v>
+        <v>37.55675842596173</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.74691438094935</v>
+        <v>21.73491242432013</v>
       </c>
       <c r="C4" t="n">
-        <v>55.97729060074463</v>
+        <v>74.94269275138453</v>
       </c>
       <c r="D4" t="n">
-        <v>25.12979598560561</v>
+        <v>39.48785616021521</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.60474089028281</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C5" t="n">
-        <v>73.0420291959627</v>
+        <v>82.95768100885549</v>
       </c>
       <c r="D5" t="n">
-        <v>25.08365384350601</v>
+        <v>30.77779052813751</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.80002656796992</v>
+        <v>11.3107153006275</v>
       </c>
       <c r="C6" t="n">
-        <v>60.86050368166828</v>
+        <v>57.03659637362695</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>28.98511922018283</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057280793200714</v>
+        <v>7.050655741967738</v>
       </c>
       <c r="C21" t="n">
-        <v>66.1620074362567</v>
+        <v>66.09989758094754</v>
       </c>
       <c r="D21" t="n">
-        <v>5.292960594900536</v>
+        <v>4.406659838729836</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.962734644967626</v>
+        <v>4.830198704894307</v>
       </c>
       <c r="C2" t="n">
-        <v>8.404742096056944</v>
+        <v>7.827474445959819</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75436745195582</v>
+        <v>22.27389191395163</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50870954171587</v>
+        <v>20.10128424445344</v>
       </c>
       <c r="C3" t="n">
-        <v>22.99743997198154</v>
+        <v>38.83793918000381</v>
       </c>
       <c r="D3" t="n">
-        <v>37.74329048976863</v>
+        <v>50.66799901617789</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.87752788334318</v>
+        <v>26.54645792283375</v>
       </c>
       <c r="C4" t="n">
-        <v>56.79410469067798</v>
+        <v>74.84059099014284</v>
       </c>
       <c r="D4" t="n">
-        <v>34.30619177720055</v>
+        <v>50.00433756810704</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.1214022246239</v>
+        <v>26.85079971115027</v>
       </c>
       <c r="C5" t="n">
-        <v>92.11247835095699</v>
+        <v>116.4598214162779</v>
       </c>
       <c r="D5" t="n">
-        <v>28.98610096788708</v>
+        <v>38.2145293878071</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.26545709524092</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>94.02786812194252</v>
+        <v>99.78385491194157</v>
       </c>
       <c r="D6" t="n">
-        <v>31.5975498611836</v>
+        <v>34.45541742824607</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>63.9588994362712</v>
+        <v>58.4493313200381</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>30.45872252425729</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
         <v>23.27821981539612</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280142056570512</v>
+        <v>7.268030827593335</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53147383691908</v>
+        <v>75.40581983628086</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370124299499198</v>
+        <v>5.451023120695001</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.196971435655114</v>
+        <v>3.631484758008952</v>
       </c>
       <c r="C2" t="n">
-        <v>9.122399667861362</v>
+        <v>8.375289664929539</v>
       </c>
       <c r="D2" t="n">
-        <v>26.09387223117598</v>
+        <v>28.94290406890022</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.63357142660446</v>
+        <v>18.17705874412969</v>
       </c>
       <c r="C3" t="n">
-        <v>28.88301745894116</v>
+        <v>33.8752045350362</v>
       </c>
       <c r="D3" t="n">
-        <v>47.98782778358409</v>
+        <v>56.3228657926395</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.49312475163494</v>
+        <v>33.57871672835365</v>
       </c>
       <c r="C4" t="n">
-        <v>57.30461349688632</v>
+        <v>86.86307337634929</v>
       </c>
       <c r="D4" t="n">
-        <v>45.51186007347363</v>
+        <v>62.90744764502287</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.02447124381072</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="C5" t="n">
-        <v>99.54921721062659</v>
+        <v>128.7807551045754</v>
       </c>
       <c r="D5" t="n">
-        <v>34.55751918948773</v>
+        <v>47.61476365597031</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.48937768726721</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>122.1235239220778</v>
+        <v>145.9122525436822</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>38.48058301565798</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>104.0829281088383</v>
+        <v>104.2625879387155</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>60.33330516448773</v>
+        <v>53.57397222074844</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489929823948049</v>
+        <v>7.470863767043044</v>
       </c>
       <c r="C21" t="n">
-        <v>84.26171051941554</v>
+        <v>84.04721737923424</v>
       </c>
       <c r="D21" t="n">
-        <v>7.489929823948049</v>
+        <v>6.537005796162664</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_41_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497639904186</v>
+        <v>10.84497635078499</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907217476596</v>
+        <v>37.789072006616</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.861614631430205</v>
+        <v>8.152432936065514</v>
       </c>
       <c r="C2" t="n">
-        <v>16.77512302246525</v>
+        <v>7.060729488943061</v>
       </c>
       <c r="D2" t="n">
-        <v>31.10765775676444</v>
+        <v>45.04356641854791</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.06000978314607</v>
+        <v>20.4841658491097</v>
       </c>
       <c r="C3" t="n">
-        <v>33.0259927708627</v>
+        <v>30.43417883165112</v>
       </c>
       <c r="D3" t="n">
-        <v>65.17332134642452</v>
+        <v>93.32493676570181</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>39.3347035183527</v>
       </c>
       <c r="C4" t="n">
-        <v>84.82103815151592</v>
+        <v>70.61613061876882</v>
       </c>
       <c r="D4" t="n">
-        <v>75.42767611728245</v>
+        <v>114.5198879526862</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>52.0817157102933</v>
       </c>
       <c r="C5" t="n">
-        <v>144.8323300690107</v>
+        <v>92.01430358053231</v>
       </c>
       <c r="D5" t="n">
-        <v>57.67767762450012</v>
+        <v>82.31954500109507</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.07177506006381</v>
+        <v>50.4353248102714</v>
       </c>
       <c r="C6" t="n">
-        <v>173.6858950968245</v>
+        <v>115.0392324882328</v>
       </c>
       <c r="D6" t="n">
-        <v>44.39757642915352</v>
+        <v>52.89067581859268</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>35.81219275551515</v>
       </c>
       <c r="C7" t="n">
-        <v>157.2622377524796</v>
+        <v>103.783495059043</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>40.3036885024443</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="C8" t="n">
-        <v>94.88100687693299</v>
+        <v>68.09402076655876</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.657341948503965</v>
+        <v>7.660101756090582</v>
       </c>
       <c r="C21" t="n">
-        <v>92.84527112561058</v>
+        <v>92.87873379259831</v>
       </c>
       <c r="D21" t="n">
-        <v>7.657341948503965</v>
+        <v>7.660101756090582</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.427502219703868</v>
+        <v>8.066039138091794</v>
       </c>
       <c r="C2" t="n">
-        <v>10.63429113240145</v>
+        <v>7.674321804097318</v>
       </c>
       <c r="D2" t="n">
-        <v>36.12340677776139</v>
+        <v>49.15316230852505</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.40853021815369</v>
+        <v>23.51285751671111</v>
       </c>
       <c r="C3" t="n">
-        <v>48.33634821859171</v>
+        <v>28.74557278034661</v>
       </c>
       <c r="D3" t="n">
-        <v>72.46279805045707</v>
+        <v>104.0848916042468</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.12827445855362</v>
+        <v>38.5817030291954</v>
       </c>
       <c r="C4" t="n">
-        <v>82.7024266057513</v>
+        <v>72.39014872034281</v>
       </c>
       <c r="D4" t="n">
-        <v>86.85031065619407</v>
+        <v>129.6181858962979</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.45491870662732</v>
+        <v>54.95332774521523</v>
       </c>
       <c r="C5" t="n">
-        <v>149.8883307458818</v>
+        <v>109.8330244126119</v>
       </c>
       <c r="D5" t="n">
-        <v>69.335931612431</v>
+        <v>100.9972950743906</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.12210623488766</v>
+        <v>59.81396062894117</v>
       </c>
       <c r="C6" t="n">
-        <v>197.3136170949325</v>
+        <v>128.3222789266921</v>
       </c>
       <c r="D6" t="n">
-        <v>50.59633143376788</v>
+        <v>63.47686131348603</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.59638818703009</v>
+        <v>46.41212271826796</v>
       </c>
       <c r="C7" t="n">
-        <v>198.2246789644735</v>
+        <v>132.7686142792259</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.02627050830318</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="C8" t="n">
-        <v>145.9515224518521</v>
+        <v>98.88653751025997</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>77.54530591534278</v>
+        <v>59.24061996966101</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>37.43894870145212</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.826199866523052</v>
+        <v>7.833046808450872</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7623232814843</v>
+        <v>100.850477658805</v>
       </c>
       <c r="D21" t="n">
-        <v>8.804474849838433</v>
+        <v>8.812177659507231</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.341108421730148</v>
+        <v>8.759153017290043</v>
       </c>
       <c r="C2" t="n">
-        <v>8.225082266179777</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="D2" t="n">
-        <v>34.97378021608837</v>
+        <v>57.81315880768617</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>24.75476836258332</v>
       </c>
       <c r="C3" t="n">
-        <v>44.73824288252715</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D3" t="n">
-        <v>81.49487692952773</v>
+        <v>114.4226949299658</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.44359539806609</v>
+        <v>40.11322944782042</v>
       </c>
       <c r="C4" t="n">
-        <v>98.71964040053801</v>
+        <v>71.86687719397926</v>
       </c>
       <c r="D4" t="n">
-        <v>97.02219861989529</v>
+        <v>145.9799931352752</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.4794623992335</v>
+        <v>55.61600744558182</v>
       </c>
       <c r="C5" t="n">
-        <v>148.9311267342412</v>
+        <v>118.3251420543468</v>
       </c>
       <c r="D5" t="n">
-        <v>79.66882619962867</v>
+        <v>116.8770641905828</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.07935130425731</v>
+        <v>65.32843748369551</v>
       </c>
       <c r="C6" t="n">
-        <v>212.3274847359789</v>
+        <v>146.3147691024234</v>
       </c>
       <c r="D6" t="n">
-        <v>58.40515267334701</v>
+        <v>75.75361635509239</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.26187426178919</v>
+        <v>56.2934133615121</v>
       </c>
       <c r="C7" t="n">
-        <v>234.5758512096201</v>
+        <v>155.4656394537079</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>51.74203100462389</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.70215489718149</v>
+        <v>36.55046702910875</v>
       </c>
       <c r="C8" t="n">
-        <v>191.6813305156685</v>
+        <v>129.9293999185441</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31249886958674</v>
+        <v>18.85937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>117.8156149958427</v>
+        <v>84.7562428030356</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>61.4966761940202</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>36.78314123501524</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
         <v>32.54493639578176</v>
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.97744755784661</v>
+        <v>7.989597463469113</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6955420309292</v>
+        <v>107.859565756833</v>
       </c>
       <c r="D21" t="n">
-        <v>9.971809447308262</v>
+        <v>9.986996829336391</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.915029918087032</v>
+        <v>8.155378179178253</v>
       </c>
       <c r="C2" t="n">
-        <v>5.790347959647687</v>
+        <v>10.50273694003238</v>
       </c>
       <c r="D2" t="n">
-        <v>28.9173786285898</v>
+        <v>47.34871002811941</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.40071729424872</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="C3" t="n">
-        <v>63.66142988188442</v>
+        <v>47.32023934469626</v>
       </c>
       <c r="D3" t="n">
-        <v>85.35805414573893</v>
+        <v>121.5992706480099</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.84977690571701</v>
+        <v>26.71237328485147</v>
       </c>
       <c r="C4" t="n">
-        <v>125.5213527264759</v>
+        <v>97.69862278812133</v>
       </c>
       <c r="D4" t="n">
-        <v>91.43212719191393</v>
+        <v>137.3013434297334</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.76520773443155</v>
+        <v>36.79099521664922</v>
       </c>
       <c r="C5" t="n">
-        <v>126.8663470812941</v>
+        <v>87.42463306317848</v>
       </c>
       <c r="D5" t="n">
-        <v>55.54237636776331</v>
+        <v>76.67449570167591</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.60005313593983</v>
+        <v>34.93843729873549</v>
       </c>
       <c r="C6" t="n">
-        <v>154.4858552448696</v>
+        <v>102.4002125437593</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="C7" t="n">
-        <v>134.8047590178338</v>
+        <v>91.32708018755953</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>86.78649705541802</v>
+        <v>62.4195190360122</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>46.92655851529327</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,7 +1839,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.621667280966483</v>
+        <v>4.948008429403925</v>
       </c>
       <c r="C2" t="n">
-        <v>2.997275741065512</v>
+        <v>4.93720920465721</v>
       </c>
       <c r="D2" t="n">
-        <v>21.24502031990098</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.80814259151115</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="C3" t="n">
-        <v>44.35045253934966</v>
+        <v>45.08185457901354</v>
       </c>
       <c r="D3" t="n">
-        <v>88.15603510284234</v>
+        <v>131.4216564289993</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.79269667015045</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="C4" t="n">
-        <v>145.3929080081356</v>
+        <v>110.8442245479861</v>
       </c>
       <c r="D4" t="n">
-        <v>109.1978336479642</v>
+        <v>161.512223564164</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.6122760767473</v>
+        <v>40.39891802975625</v>
       </c>
       <c r="C5" t="n">
-        <v>173.0575765661065</v>
+        <v>129.3207163419111</v>
       </c>
       <c r="D5" t="n">
-        <v>68.77142668248908</v>
+        <v>97.38937226128361</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.22899356146354</v>
+        <v>40.89568236810514</v>
       </c>
       <c r="C6" t="n">
-        <v>181.4544646805295</v>
+        <v>121.0367292134765</v>
       </c>
       <c r="D6" t="n">
-        <v>35.82397372796611</v>
+        <v>42.54600025894403</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="C7" t="n">
-        <v>168.580807034741</v>
+        <v>114.8625179014683</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>114.9086600435679</v>
+        <v>81.19544387973245</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>42.48905889209769</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
         <v>29.60951076008381</v>
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.224460371374025</v>
+        <v>5.7402788267311</v>
       </c>
       <c r="C2" t="n">
-        <v>4.824308218668826</v>
+        <v>4.676064315327558</v>
       </c>
       <c r="D2" t="n">
-        <v>17.81086685044563</v>
+        <v>32.19445246536565</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6062624173348</v>
+        <v>22.94344384824796</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58711048933537</v>
+        <v>31.94607029619121</v>
       </c>
       <c r="D3" t="n">
-        <v>85.53476873250335</v>
+        <v>126.6650888019235</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.42556408649115</v>
+        <v>46.17552152154448</v>
       </c>
       <c r="C4" t="n">
-        <v>129.6054231761427</v>
+        <v>111.5334114363674</v>
       </c>
       <c r="D4" t="n">
-        <v>124.3088943117311</v>
+        <v>186.0038835420092</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.71736413883072</v>
+        <v>47.76202581160733</v>
       </c>
       <c r="C5" t="n">
-        <v>216.4999124790279</v>
+        <v>164.4427404613408</v>
       </c>
       <c r="D5" t="n">
-        <v>86.34471058850698</v>
+        <v>127.1608713925681</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.54221213684728</v>
+        <v>46.85292743747478</v>
       </c>
       <c r="C6" t="n">
-        <v>222.9941735426206</v>
+        <v>160.4028486583651</v>
       </c>
       <c r="D6" t="n">
-        <v>46.41015922285948</v>
+        <v>58.84792088796232</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.47555110394973</v>
+        <v>32.5184292077671</v>
       </c>
       <c r="C7" t="n">
-        <v>211.8788260351381</v>
+        <v>141.6318325531661</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>161.806747875438</v>
+        <v>112.8224461720434</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>86.64218014289374</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2464,7 +2464,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
         <v>29.852984190737</v>
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.537817815478005</v>
+        <v>3.494040079414398</v>
       </c>
       <c r="C2" t="n">
-        <v>2.397427893770711</v>
+        <v>2.283545160078081</v>
       </c>
       <c r="D2" t="n">
-        <v>12.61251275645877</v>
+        <v>22.48594941806894</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15113239319178</v>
+        <v>23.39995653072273</v>
       </c>
       <c r="C3" t="n">
-        <v>25.79542092908494</v>
+        <v>28.33323874456295</v>
       </c>
       <c r="D3" t="n">
-        <v>84.09159960726055</v>
+        <v>127.3915821030661</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.39927788265474</v>
+        <v>50.47655821384976</v>
       </c>
       <c r="C4" t="n">
-        <v>122.1264691651905</v>
+        <v>111.1632925518663</v>
       </c>
       <c r="D4" t="n">
-        <v>134.889189320399</v>
+        <v>202.9272504678157</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.06726723217008</v>
+        <v>49.72552122010096</v>
       </c>
       <c r="C5" t="n">
-        <v>257.7087723647878</v>
+        <v>199.4175024251334</v>
       </c>
       <c r="D5" t="n">
-        <v>89.14269154561039</v>
+        <v>134.1312800927205</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.33716573537994</v>
+        <v>38.35982804803563</v>
       </c>
       <c r="C6" t="n">
-        <v>260.1062002585585</v>
+        <v>188.2569945232556</v>
       </c>
       <c r="D6" t="n">
-        <v>45.56487444950297</v>
+        <v>56.51332484726341</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.246279805045708</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>215.7115690725177</v>
+        <v>147.9199265988669</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>109.8182981970482</v>
+        <v>81.44578954431539</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
         <v>23.34596040698915</v>
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.487748682561417</v>
+        <v>4.05363627083508</v>
       </c>
       <c r="C2" t="n">
-        <v>10.87383757223767</v>
+        <v>6.265513848503144</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59564311903733</v>
+        <v>19.14800722362979</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.16032797542849</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="C3" t="n">
-        <v>17.72545480017616</v>
+        <v>18.79555979780518</v>
       </c>
       <c r="D3" t="n">
-        <v>75.87928006123597</v>
+        <v>117.1175923781232</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>47.553895298307</v>
       </c>
       <c r="C4" t="n">
-        <v>95.91184196639215</v>
+        <v>91.92987327796708</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6444153468721</v>
+        <v>216.4557338323368</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.89041377668541</v>
+        <v>60.27930904075417</v>
       </c>
       <c r="C5" t="n">
-        <v>242.6880324898116</v>
+        <v>203.3690369347268</v>
       </c>
       <c r="D5" t="n">
-        <v>111.7965198211056</v>
+        <v>168.1979254300848</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.91076843656734</v>
+        <v>49.1875234781737</v>
       </c>
       <c r="C6" t="n">
-        <v>328.4132602769388</v>
+        <v>244.3678028117779</v>
       </c>
       <c r="D6" t="n">
-        <v>57.51961624411638</v>
+        <v>76.15613291383359</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>281.4670668075605</v>
+        <v>201.2190094624262</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>177.3281790795801</v>
+        <v>125.7569721754952</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>68.22655670663207</v>
+        <v>54.35937038414588</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>24.62714116103124</v>
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.758310138306037</v>
+        <v>2.929535149472482</v>
       </c>
       <c r="C2" t="n">
-        <v>6.510950774564847</v>
+        <v>3.891647899634356</v>
       </c>
       <c r="D2" t="n">
-        <v>10.79235251278519</v>
+        <v>13.90743797836032</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.35391219961436</v>
+        <v>16.39518666092173</v>
       </c>
       <c r="C3" t="n">
-        <v>28.47559216167874</v>
+        <v>21.34810382884689</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5448639469863</v>
+        <v>108.5371174430061</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>43.17628228507048</v>
       </c>
       <c r="C4" t="n">
-        <v>77.53352494289186</v>
+        <v>76.12962572581891</v>
       </c>
       <c r="D4" t="n">
-        <v>147.3456041918825</v>
+        <v>222.9391956711827</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.22835597112457</v>
+        <v>65.92435834017333</v>
       </c>
       <c r="C5" t="n">
-        <v>227.3727683035613</v>
+        <v>196.0550165380881</v>
       </c>
       <c r="D5" t="n">
-        <v>127.8971821707532</v>
+        <v>192.4961811101934</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.50574860306991</v>
+        <v>56.75483478250812</v>
       </c>
       <c r="C6" t="n">
-        <v>361.8221346524578</v>
+        <v>280.4332864749887</v>
       </c>
       <c r="D6" t="n">
-        <v>67.62278186852032</v>
+        <v>92.05553698411069</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.41460063082842</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
-        <v>342.5514089657971</v>
+        <v>251.5237618280328</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>227.5642091058894</v>
+        <v>160.3881224428014</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>60.34999487545991</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.778346003018473</v>
+        <v>3.529382996767283</v>
       </c>
       <c r="C2" t="n">
-        <v>7.363107781851078</v>
+        <v>6.728898764907639</v>
       </c>
       <c r="D2" t="n">
-        <v>11.66316272645211</v>
+        <v>12.20606920690059</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.845546815263761</v>
+        <v>13.31740760810798</v>
       </c>
       <c r="C3" t="n">
-        <v>27.06678420608456</v>
+        <v>18.4224956701914</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10950774564847</v>
+        <v>97.39428099980483</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.17183121043897</v>
+        <v>37.35648189429538</v>
       </c>
       <c r="C4" t="n">
-        <v>73.79404793741575</v>
+        <v>66.22575488537709</v>
       </c>
       <c r="D4" t="n">
-        <v>148.0603165205742</v>
+        <v>224.1133659254619</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.71293842639499</v>
+        <v>65.87527095496098</v>
       </c>
       <c r="C5" t="n">
-        <v>192.5698121880119</v>
+        <v>172.9103144104695</v>
       </c>
       <c r="D5" t="n">
-        <v>143.4087958978529</v>
+        <v>214.2664364518664</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.2340665309008</v>
+        <v>67.22026530977911</v>
       </c>
       <c r="C6" t="n">
-        <v>362.9491810169332</v>
+        <v>293.1528097312104</v>
       </c>
       <c r="D6" t="n">
-        <v>82.47564288607032</v>
+        <v>118.7826364845259</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>34.07548106670254</v>
       </c>
       <c r="C7" t="n">
-        <v>414.8345471863769</v>
+        <v>309.8533199281528</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>55.75443387188061</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>308.175513101595</v>
+        <v>225.227649569782</v>
       </c>
       <c r="D8" t="n">
-        <v>35.46563581591602</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>142.8874878668977</v>
+        <v>106.7218659378537</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.11545498513618</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.932300466135975</v>
+        <v>8.401796852944203</v>
       </c>
       <c r="C2" t="n">
-        <v>9.642725951112171</v>
+        <v>6.515859513086081</v>
       </c>
       <c r="D2" t="n">
-        <v>11.40005434171396</v>
+        <v>14.76646721957628</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.050870954171587</v>
+        <v>2.582978209873358</v>
       </c>
       <c r="C2" t="n">
-        <v>4.358959806855839</v>
+        <v>3.98295043612931</v>
       </c>
       <c r="D2" t="n">
-        <v>8.67668621013331</v>
+        <v>9.081166264282997</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.98223073033232</v>
+        <v>17.38675184221101</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1031499288707</v>
+        <v>23.51285751671111</v>
       </c>
       <c r="D3" t="n">
-        <v>70.14096472991336</v>
+        <v>103.5351128898686</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.57795596482766</v>
+        <v>50.74457533710914</v>
       </c>
       <c r="C4" t="n">
-        <v>108.4703585991173</v>
+        <v>95.96289284701298</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3748766965607</v>
+        <v>224.674925612291</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.74066404182538</v>
+        <v>38.4599663138688</v>
       </c>
       <c r="C5" t="n">
-        <v>300.1693605734623</v>
+        <v>253.1927329252524</v>
       </c>
       <c r="D5" t="n">
-        <v>126.9890655443249</v>
+        <v>190.4590546238812</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.33588088803943</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>333.6862271964484</v>
+        <v>255.7992730800277</v>
       </c>
       <c r="D6" t="n">
-        <v>67.34102027740147</v>
+        <v>89.31842438467058</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.431609136970102</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>216.7296414418216</v>
+        <v>158.4000833417016</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54217107911827</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>105.3120762345553</v>
+        <v>78.60853867904211</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.72030938194344</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.893431468593603</v>
+        <v>7.329728359906686</v>
       </c>
       <c r="C2" t="n">
-        <v>8.980046250745575</v>
+        <v>5.493860152965151</v>
       </c>
       <c r="D2" t="n">
-        <v>13.50884841043611</v>
+        <v>25.20048182031137</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.4801567428347</v>
+        <v>17.83835578616454</v>
       </c>
       <c r="C3" t="n">
-        <v>24.29825568010856</v>
+        <v>16.4197303535279</v>
       </c>
       <c r="D3" t="n">
-        <v>12.7136327699962</v>
+        <v>15.54106615822701</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3975429874824</v>
+        <v>13.39690753270857</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14007799329019</v>
+        <v>70.13675120065075</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576181527939105</v>
+        <v>1.576106768553949</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.277474747403353</v>
+        <v>6.009277697694727</v>
       </c>
       <c r="C2" t="n">
-        <v>9.780170629706724</v>
+        <v>7.469136533909733</v>
       </c>
       <c r="D2" t="n">
-        <v>18.05237678569035</v>
+        <v>24.88239556413541</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.39518666092173</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="C3" t="n">
-        <v>31.00850123863551</v>
+        <v>19.55150553007523</v>
       </c>
       <c r="D3" t="n">
-        <v>20.98485717827557</v>
+        <v>32.95236169304419</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.27773678931061</v>
+        <v>20.58626761035137</v>
       </c>
       <c r="C4" t="n">
-        <v>37.57344813693393</v>
+        <v>25.5764911910379</v>
       </c>
       <c r="D4" t="n">
-        <v>21.73491242432013</v>
+        <v>23.21538796232432</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43928530579344</v>
+        <v>15.4363194148629</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13496012705814</v>
+        <v>86.11841357765616</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25037585385125</v>
+        <v>3.24975145576061</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.393721887131976</v>
+        <v>6.615016031215008</v>
       </c>
       <c r="C2" t="n">
-        <v>11.6337102953247</v>
+        <v>6.332272692391927</v>
       </c>
       <c r="D2" t="n">
-        <v>15.69912753861074</v>
+        <v>27.61165418194154</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50670498857837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="C3" t="n">
-        <v>35.58344554042564</v>
+        <v>25.21128104505809</v>
       </c>
       <c r="D3" t="n">
-        <v>30.55689729468197</v>
+        <v>45.20948178056562</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.3302524437212</v>
+        <v>33.60424216866407</v>
       </c>
       <c r="C4" t="n">
-        <v>60.39319177444678</v>
+        <v>38.84972015245478</v>
       </c>
       <c r="D4" t="n">
-        <v>27.37603473292231</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.97103059495811</v>
+        <v>17.37693436516855</v>
       </c>
       <c r="C5" t="n">
-        <v>41.8469958935203</v>
+        <v>29.28062527916113</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48326621686347</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72943174131654</v>
+        <v>16.72433288515925</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0495336220309</v>
+        <v>102.0184305994714</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182357935329136</v>
+        <v>4.181083221289812</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.928373475318988</v>
+        <v>6.516841260790327</v>
       </c>
       <c r="C2" t="n">
-        <v>6.335217935504667</v>
+        <v>4.985314842165304</v>
       </c>
       <c r="D2" t="n">
-        <v>16.00543282233575</v>
+        <v>30.43319708394688</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.05786636128833</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="C3" t="n">
-        <v>40.96342295969816</v>
+        <v>24.81858196335937</v>
       </c>
       <c r="D3" t="n">
-        <v>35.69143778789279</v>
+        <v>56.13633372883262</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.72513600500667</v>
+        <v>37.66278717802039</v>
       </c>
       <c r="C4" t="n">
-        <v>75.51701515836891</v>
+        <v>51.76559294952582</v>
       </c>
       <c r="D4" t="n">
-        <v>36.02915899815369</v>
+        <v>48.58767563087889</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.97289627937537</v>
+        <v>33.91938318172731</v>
       </c>
       <c r="C5" t="n">
-        <v>79.47247665877931</v>
+        <v>52.20443417332415</v>
       </c>
       <c r="D5" t="n">
-        <v>33.08489763311751</v>
+        <v>35.85833489761475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.30442390377452</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>40.25165587411923</v>
+        <v>29.98748362621883</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>38.48058301565798</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,7 +5543,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
         <v>33.9468721174462</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04863349128367</v>
+        <v>18.04168963094358</v>
       </c>
       <c r="C21" t="n">
-        <v>117.745847062184</v>
+        <v>117.7005466399652</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016211163761224</v>
+        <v>6.013896543647858</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.712209053935443</v>
+        <v>6.441246687563323</v>
       </c>
       <c r="C2" t="n">
-        <v>11.28224461720434</v>
+        <v>6.313619486011237</v>
       </c>
       <c r="D2" t="n">
-        <v>26.41195848735194</v>
+        <v>33.95767134219292</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.01583113645496</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C3" t="n">
-        <v>29.76659039276329</v>
+        <v>20.39089981720625</v>
       </c>
       <c r="D3" t="n">
-        <v>37.55675842596173</v>
+        <v>62.82694433327463</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.73491242432013</v>
+        <v>29.09900195387546</v>
       </c>
       <c r="C4" t="n">
-        <v>74.94269275138453</v>
+        <v>48.0005905037393</v>
       </c>
       <c r="D4" t="n">
-        <v>39.48785616021521</v>
+        <v>56.60266388834985</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.21771131063132</v>
+        <v>27.56256679672921</v>
       </c>
       <c r="C5" t="n">
-        <v>82.95768100885549</v>
+        <v>55.32148313430778</v>
       </c>
       <c r="D5" t="n">
-        <v>30.77779052813751</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.3107153006275</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="C6" t="n">
-        <v>57.03659637362695</v>
+        <v>38.68184129502858</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>31.91956310817655</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15237618280328</v>
+        <v>20.54110721595601</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050655741967738</v>
+        <v>7.047725173015727</v>
       </c>
       <c r="C21" t="n">
-        <v>66.09989758094754</v>
+        <v>66.07242349702244</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406659838729836</v>
+        <v>4.404828233134829</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.830198704894307</v>
+        <v>6.058365082907066</v>
       </c>
       <c r="C2" t="n">
-        <v>7.827474445959819</v>
+        <v>10.64214511403543</v>
       </c>
       <c r="D2" t="n">
-        <v>22.27389191395163</v>
+        <v>29.57024085191393</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.10128424445344</v>
+        <v>21.4364611222291</v>
       </c>
       <c r="C3" t="n">
-        <v>38.83793918000381</v>
+        <v>23.09561474240621</v>
       </c>
       <c r="D3" t="n">
-        <v>50.66799901617789</v>
+        <v>76.16889563398878</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.54645792283375</v>
+        <v>35.03366682604742</v>
       </c>
       <c r="C4" t="n">
-        <v>74.84059099014284</v>
+        <v>49.97881212779662</v>
       </c>
       <c r="D4" t="n">
-        <v>50.00433756810704</v>
+        <v>76.39764284907828</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.85079971115027</v>
+        <v>36.81553890925539</v>
       </c>
       <c r="C5" t="n">
-        <v>116.4598214162779</v>
+        <v>74.93189352663781</v>
       </c>
       <c r="D5" t="n">
-        <v>38.2145293878071</v>
+        <v>48.47379289718628</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.80381469006666</v>
+        <v>28.53842401475054</v>
       </c>
       <c r="C6" t="n">
-        <v>99.78385491194157</v>
+        <v>67.66303352439442</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="C7" t="n">
-        <v>58.4493313200381</v>
+        <v>41.20198765183014</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>27.45457454926205</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
         <v>23.27821981539612</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268030827593335</v>
+        <v>7.265855849725813</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40581983628086</v>
+        <v>75.3832544409053</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451023120695001</v>
+        <v>5.449391887294359</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.631484758008952</v>
+        <v>5.912084674974292</v>
       </c>
       <c r="C2" t="n">
-        <v>8.375289664929539</v>
+        <v>7.121597846606362</v>
       </c>
       <c r="D2" t="n">
-        <v>28.94290406890022</v>
+        <v>39.7980884347572</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17705874412969</v>
+        <v>21.12721059539136</v>
       </c>
       <c r="C3" t="n">
-        <v>33.8752045350362</v>
+        <v>33.99792299806705</v>
       </c>
       <c r="D3" t="n">
-        <v>56.3228657926395</v>
+        <v>82.15264789137309</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.57871672835365</v>
+        <v>38.60722846950582</v>
       </c>
       <c r="C4" t="n">
-        <v>86.86307337634929</v>
+        <v>54.53510322320607</v>
       </c>
       <c r="D4" t="n">
-        <v>62.90744764502287</v>
+        <v>97.41784294470675</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.64940256305943</v>
+        <v>45.67581194008286</v>
       </c>
       <c r="C5" t="n">
-        <v>128.7807551045754</v>
+        <v>84.74937056910592</v>
       </c>
       <c r="D5" t="n">
-        <v>47.61476365597031</v>
+        <v>64.94261063592651</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.73968229412113</v>
+        <v>39.84913931537804</v>
       </c>
       <c r="C6" t="n">
-        <v>145.9122525436822</v>
+        <v>94.83290123942491</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>43.14977509705582</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>104.2625879387155</v>
+        <v>72.04359178074368</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>53.57397222074844</v>
+        <v>40.63944621729671</v>
       </c>
       <c r="D8" t="n">
         <v>33.71321616383547</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.470863767043044</v>
+        <v>7.470783268994486</v>
       </c>
       <c r="C21" t="n">
-        <v>84.04721737923424</v>
+        <v>84.04631177618796</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537005796162664</v>
+        <v>6.536935360370175</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_41_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635078499</v>
+        <v>10.84497647184259</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789072006616</v>
+        <v>37.78907242843844</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.152432936065514</v>
+        <v>1.142754327743287</v>
       </c>
       <c r="C2" t="n">
-        <v>7.060729488943061</v>
+        <v>4.018293353482195</v>
       </c>
       <c r="D2" t="n">
-        <v>45.04356641854791</v>
+        <v>11.87522023056942</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.4841658491097</v>
+        <v>9.090983741325465</v>
       </c>
       <c r="C3" t="n">
-        <v>30.43417883165112</v>
+        <v>45.47455366071226</v>
       </c>
       <c r="D3" t="n">
-        <v>93.32493676570181</v>
+        <v>63.32272692391927</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3347035183527</v>
+        <v>15.04724706299086</v>
       </c>
       <c r="C4" t="n">
-        <v>70.61613061876882</v>
+        <v>126.6444721001343</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5198879526862</v>
+        <v>81.1964256274367</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.0817157102933</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="C5" t="n">
-        <v>92.01430358053231</v>
+        <v>124.1419972020092</v>
       </c>
       <c r="D5" t="n">
-        <v>82.31954500109507</v>
+        <v>51.3454049321082</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.4353248102714</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="C6" t="n">
-        <v>115.0392324882328</v>
+        <v>75.02908654935825</v>
       </c>
       <c r="D6" t="n">
-        <v>52.89067581859268</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.81219275551515</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>103.783495059043</v>
+        <v>41.62119392154352</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.69247628885927</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>68.09402076655876</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660101756090582</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.87873379259831</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660101756090582</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.066039138091794</v>
+        <v>1.646390900021901</v>
       </c>
       <c r="C2" t="n">
-        <v>7.674321804097318</v>
+        <v>5.37703217615978</v>
       </c>
       <c r="D2" t="n">
-        <v>49.15316230852505</v>
+        <v>16.73978010511236</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.51285751671111</v>
+        <v>6.327363953870693</v>
       </c>
       <c r="C3" t="n">
-        <v>28.74557278034661</v>
+        <v>28.36759991421159</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0848916042468</v>
+        <v>58.26181750852697</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.5817030291954</v>
+        <v>16.56601076146068</v>
       </c>
       <c r="C4" t="n">
-        <v>72.39014872034281</v>
+        <v>119.4845860930623</v>
       </c>
       <c r="D4" t="n">
-        <v>129.6181858962979</v>
+        <v>93.94638306249003</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.95332774521523</v>
+        <v>18.94773069196344</v>
       </c>
       <c r="C5" t="n">
-        <v>109.8330244126119</v>
+        <v>184.6421994762189</v>
       </c>
       <c r="D5" t="n">
-        <v>100.9972950743906</v>
+        <v>67.88785374866696</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.81396062894117</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C6" t="n">
-        <v>128.3222789266921</v>
+        <v>137.9021730247325</v>
       </c>
       <c r="D6" t="n">
-        <v>63.47686131348603</v>
+        <v>39.00385454202154</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.41212271826796</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>132.7686142792259</v>
+        <v>74.91814905877834</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.45457454926205</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>42.05807164993335</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>59.24061996966101</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>37.43894870145212</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.833046808450872</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.850477658805</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.812177659507231</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.759153017290043</v>
+        <v>0.8835729338221293</v>
       </c>
       <c r="C2" t="n">
-        <v>15.09142570968197</v>
+        <v>2.264891953697392</v>
       </c>
       <c r="D2" t="n">
-        <v>57.81315880768617</v>
+        <v>11.43048852054561</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.75476836258332</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C3" t="n">
-        <v>28.95664853675967</v>
+        <v>26.65935890882213</v>
       </c>
       <c r="D3" t="n">
-        <v>114.4226949299658</v>
+        <v>59.81788761975815</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.11322944782042</v>
+        <v>18.08477445993049</v>
       </c>
       <c r="C4" t="n">
-        <v>71.86687719397926</v>
+        <v>112.0566829627309</v>
       </c>
       <c r="D4" t="n">
-        <v>145.9799931352752</v>
+        <v>101.6678287563912</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.61600744558182</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3251420543468</v>
+        <v>219.9114857512856</v>
       </c>
       <c r="D5" t="n">
-        <v>116.8770641905828</v>
+        <v>75.93818492349079</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.32843748369551</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>146.3147691024234</v>
+        <v>176.6645176315093</v>
       </c>
       <c r="D6" t="n">
-        <v>75.75361635509239</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.2934133615121</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>155.4656394537079</v>
+        <v>72.04359178074368</v>
       </c>
       <c r="D7" t="n">
-        <v>51.74203100462389</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.55046702910875</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>129.9293999185441</v>
+        <v>40.13875488813084</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.85937339858122</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>84.7562428030356</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.989597463469113</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.859565756833</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.986996829336391</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.155378179178253</v>
+        <v>0.7490734983403163</v>
       </c>
       <c r="C2" t="n">
-        <v>10.50273694003238</v>
+        <v>5.355433726666351</v>
       </c>
       <c r="D2" t="n">
-        <v>47.34871002811941</v>
+        <v>10.89347252632261</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.53940576245478</v>
+        <v>4.790928796724435</v>
       </c>
       <c r="C3" t="n">
-        <v>47.32023934469626</v>
+        <v>16.75352457297182</v>
       </c>
       <c r="D3" t="n">
-        <v>121.5992706480099</v>
+        <v>55.31657439578653</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.71237328485147</v>
+        <v>15.67262035059608</v>
       </c>
       <c r="C4" t="n">
-        <v>97.69862278812133</v>
+        <v>88.63709147792328</v>
       </c>
       <c r="D4" t="n">
-        <v>137.3013434297334</v>
+        <v>107.8832734719777</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.79099521664922</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="C5" t="n">
-        <v>87.42463306317848</v>
+        <v>215.2727278487194</v>
       </c>
       <c r="D5" t="n">
-        <v>76.67449570167591</v>
+        <v>93.14331344041615</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.93843729873549</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>102.4002125437593</v>
+        <v>263.1250744491174</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>52.40765594810324</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.19419042345839</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>91.32708018755953</v>
+        <v>155.6452992835851</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>62.4195190360122</v>
+        <v>64.50573290753667</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.948008429403925</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C2" t="n">
-        <v>4.93720920465721</v>
+        <v>3.542145716922492</v>
       </c>
       <c r="D2" t="n">
-        <v>32.27888276793088</v>
+        <v>7.902087271482576</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.01064466049325</v>
+        <v>3.858268477689965</v>
       </c>
       <c r="C3" t="n">
-        <v>45.08185457901354</v>
+        <v>19.01645303126072</v>
       </c>
       <c r="D3" t="n">
-        <v>131.4216564289993</v>
+        <v>52.10625940289946</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.14777054391831</v>
+        <v>13.47743248390021</v>
       </c>
       <c r="C4" t="n">
-        <v>110.8442245479861</v>
+        <v>68.99526515905734</v>
       </c>
       <c r="D4" t="n">
-        <v>161.512223564164</v>
+        <v>110.8059363875205</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.39891802975625</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>129.3207163419111</v>
+        <v>200.9882987519283</v>
       </c>
       <c r="D5" t="n">
-        <v>97.38937226128361</v>
+        <v>106.3478200625358</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>21.69564251615027</v>
       </c>
       <c r="C6" t="n">
-        <v>121.0367292134765</v>
+        <v>305.0672998699496</v>
       </c>
       <c r="D6" t="n">
-        <v>42.54600025894403</v>
+        <v>62.39006660488482</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>114.8625179014683</v>
+        <v>233.2583457905209</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>81.19544387973245</v>
+        <v>100.8893028269235</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.7402788267311</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C2" t="n">
-        <v>4.676064315327558</v>
+        <v>9.419869222248145</v>
       </c>
       <c r="D2" t="n">
-        <v>32.19445246536565</v>
+        <v>11.82122410683584</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.94344384824796</v>
+        <v>2.645810062945154</v>
       </c>
       <c r="C3" t="n">
-        <v>31.94607029619121</v>
+        <v>16.25283324380595</v>
       </c>
       <c r="D3" t="n">
-        <v>126.6650888019235</v>
+        <v>47.38896168399354</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.17552152154448</v>
+        <v>10.64410860944392</v>
       </c>
       <c r="C4" t="n">
-        <v>111.5334114363674</v>
+        <v>58.35115654961343</v>
       </c>
       <c r="D4" t="n">
-        <v>186.0038835420092</v>
+        <v>110.1550376596049</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.76202581160733</v>
+        <v>23.12015843501239</v>
       </c>
       <c r="C5" t="n">
-        <v>164.4427404613408</v>
+        <v>167.9034011188108</v>
       </c>
       <c r="D5" t="n">
-        <v>127.1608713925681</v>
+        <v>119.503239299443</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.85292743747478</v>
+        <v>26.44533790929634</v>
       </c>
       <c r="C6" t="n">
-        <v>160.4028486583651</v>
+        <v>312.59435951841</v>
       </c>
       <c r="D6" t="n">
-        <v>58.84792088796232</v>
+        <v>77.68569583705012</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.5184292077671</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>141.6318325531661</v>
+        <v>326.202364446975</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>112.8224461720434</v>
+        <v>187.4254542177586</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>41.22358610132356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>77.65624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.494040079414398</v>
+        <v>0.5684319207589033</v>
       </c>
       <c r="C2" t="n">
-        <v>2.283545160078081</v>
+        <v>5.049128442941345</v>
       </c>
       <c r="D2" t="n">
-        <v>22.48594941806894</v>
+        <v>8.605018627723293</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39995653072273</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C3" t="n">
-        <v>28.33323874456295</v>
+        <v>25.69233742013903</v>
       </c>
       <c r="D3" t="n">
-        <v>127.3915821030661</v>
+        <v>52.1847992192392</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.47655821384976</v>
+        <v>16.42562083975339</v>
       </c>
       <c r="C4" t="n">
-        <v>111.1632925518663</v>
+        <v>86.40361545076178</v>
       </c>
       <c r="D4" t="n">
-        <v>202.9272504678157</v>
+        <v>113.1159887356133</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.72552122010096</v>
+        <v>16.1742934274662</v>
       </c>
       <c r="C5" t="n">
-        <v>199.4175024251334</v>
+        <v>256.3834129640546</v>
       </c>
       <c r="D5" t="n">
-        <v>134.1312800927205</v>
+        <v>111.0602090429204</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.35982804803563</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>188.2569945232556</v>
+        <v>288.3628626821902</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>65.73095404243671</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>147.9199265988669</v>
+        <v>131.810428519881</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>81.44578954431539</v>
+        <v>57.24570863463151</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.05363627083508</v>
+        <v>0.3436116964863836</v>
       </c>
       <c r="C2" t="n">
-        <v>6.265513848503144</v>
+        <v>3.212278488295564</v>
       </c>
       <c r="D2" t="n">
-        <v>19.14800722362979</v>
+        <v>6.218389958699297</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01016163440774</v>
+        <v>2.920699420134261</v>
       </c>
       <c r="C3" t="n">
-        <v>18.79555979780518</v>
+        <v>22.47220495020949</v>
       </c>
       <c r="D3" t="n">
-        <v>117.1175923781232</v>
+        <v>47.1238898038469</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.553895298307</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C4" t="n">
-        <v>91.92987327796708</v>
+        <v>72.59435224282615</v>
       </c>
       <c r="D4" t="n">
-        <v>216.4557338323368</v>
+        <v>109.9253086968111</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.27930904075417</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3690369347268</v>
+        <v>190.6554041647306</v>
       </c>
       <c r="D5" t="n">
-        <v>168.1979254300848</v>
+        <v>111.7474324358932</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.1875234781737</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>244.3678028117779</v>
+        <v>281.6408361512123</v>
       </c>
       <c r="D6" t="n">
-        <v>76.15613291383359</v>
+        <v>69.11209313586272</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>201.2190094624262</v>
+        <v>182.3547273253238</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>125.7569721754952</v>
+        <v>67.76022654711485</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.929535149472482</v>
+        <v>0.1943860454408685</v>
       </c>
       <c r="C2" t="n">
-        <v>3.891647899634356</v>
+        <v>8.942739837984195</v>
       </c>
       <c r="D2" t="n">
-        <v>13.90743797836032</v>
+        <v>6.617961274327748</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.39518666092173</v>
+        <v>1.963495408493621</v>
       </c>
       <c r="C3" t="n">
-        <v>21.34810382884689</v>
+        <v>16.59644494029233</v>
       </c>
       <c r="D3" t="n">
-        <v>108.5371174430061</v>
+        <v>41.36593951843935</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.17628228507048</v>
+        <v>8.423395302437632</v>
       </c>
       <c r="C4" t="n">
-        <v>76.12962572581891</v>
+        <v>63.32861741014475</v>
       </c>
       <c r="D4" t="n">
-        <v>222.9391956711827</v>
+        <v>108.878765644084</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.92435834017333</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C5" t="n">
-        <v>196.0550165380881</v>
+        <v>161.5465847338127</v>
       </c>
       <c r="D5" t="n">
-        <v>192.4961811101934</v>
+        <v>125.5655313731671</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.75483478250812</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C6" t="n">
-        <v>280.4332864749887</v>
+        <v>294.0785978163151</v>
       </c>
       <c r="D6" t="n">
-        <v>92.05553698411069</v>
+        <v>86.78257006460107</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>251.5237618280328</v>
+        <v>300.0319158948677</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>160.3881224428014</v>
+        <v>154.212929383089</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>60.34999487545991</v>
+        <v>55.57968278052466</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.529382996767283</v>
+        <v>0.300414797499524</v>
       </c>
       <c r="C2" t="n">
-        <v>6.728898764907639</v>
+        <v>19.27268918206914</v>
       </c>
       <c r="D2" t="n">
-        <v>12.20606920690059</v>
+        <v>7.32874661220244</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.31740760810798</v>
+        <v>1.286089492563322</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4224956701914</v>
+        <v>26.24702487303848</v>
       </c>
       <c r="D3" t="n">
-        <v>97.39428099980483</v>
+        <v>37.32604771546373</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.35648189429538</v>
+        <v>6.100580234189679</v>
       </c>
       <c r="C4" t="n">
-        <v>66.22575488537709</v>
+        <v>51.93150831154353</v>
       </c>
       <c r="D4" t="n">
-        <v>224.1133659254619</v>
+        <v>105.330729440936</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.87527095496098</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C5" t="n">
-        <v>172.9103144104695</v>
+        <v>139.0891059991669</v>
       </c>
       <c r="D5" t="n">
-        <v>214.2664364518664</v>
+        <v>135.4075521082413</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.22026530977911</v>
+        <v>18.79752329321368</v>
       </c>
       <c r="C6" t="n">
-        <v>293.1528097312104</v>
+        <v>274.798054652612</v>
       </c>
       <c r="D6" t="n">
-        <v>118.7826364845259</v>
+        <v>103.0442390377452</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.07548106670254</v>
+        <v>11.85754877189298</v>
       </c>
       <c r="C7" t="n">
-        <v>309.8533199281528</v>
+        <v>363.2122894016712</v>
       </c>
       <c r="D7" t="n">
-        <v>55.75443387188061</v>
+        <v>57.61091878061132</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>225.227649569782</v>
+        <v>270.4567663044325</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>106.7218659378537</v>
+        <v>118.481239939322</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.401796852944203</v>
+        <v>2.91480893390878</v>
       </c>
       <c r="C2" t="n">
-        <v>6.515859513086081</v>
+        <v>9.804714322312895</v>
       </c>
       <c r="D2" t="n">
-        <v>14.76646721957628</v>
+        <v>17.89627890071511</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.582978209873358</v>
+        <v>0.1737693436516854</v>
       </c>
       <c r="C2" t="n">
-        <v>3.98295043612931</v>
+        <v>24.49558696866217</v>
       </c>
       <c r="D2" t="n">
-        <v>9.081166264282997</v>
+        <v>13.75330358879357</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.38675184221101</v>
+        <v>1.133918598405066</v>
       </c>
       <c r="C3" t="n">
-        <v>23.51285751671111</v>
+        <v>49.58316780298516</v>
       </c>
       <c r="D3" t="n">
-        <v>103.5351128898686</v>
+        <v>34.78822989998573</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.74457533710914</v>
+        <v>4.377613013236528</v>
       </c>
       <c r="C4" t="n">
-        <v>95.96289284701298</v>
+        <v>58.19800390775092</v>
       </c>
       <c r="D4" t="n">
-        <v>224.674925612291</v>
+        <v>100.8510146664578</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.4599663138688</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>253.1927329252524</v>
+        <v>117.9078992800419</v>
       </c>
       <c r="D5" t="n">
-        <v>190.4590546238812</v>
+        <v>139.6536109291088</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.1321193339126</v>
+        <v>19.44154978719959</v>
       </c>
       <c r="C6" t="n">
-        <v>255.7992730800277</v>
+        <v>252.5388889542241</v>
       </c>
       <c r="D6" t="n">
-        <v>89.31842438467058</v>
+        <v>118.8228881404</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>158.4000833417016</v>
+        <v>381.8370250989374</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>69.58824077242241</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>78.60853867904211</v>
+        <v>359.9970656702629</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>210.5593571206303</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>82.56498192715677</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.329728359906686</v>
+        <v>5.125704763872597</v>
       </c>
       <c r="C2" t="n">
-        <v>5.493860152965151</v>
+        <v>7.65468685001238</v>
       </c>
       <c r="D2" t="n">
-        <v>25.20048182031137</v>
+        <v>22.93755336202248</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.83835578616454</v>
+        <v>4.71238898038469</v>
       </c>
       <c r="C3" t="n">
-        <v>16.4197303535279</v>
+        <v>19.35515598922587</v>
       </c>
       <c r="D3" t="n">
-        <v>15.54106615822701</v>
+        <v>15.18272824617692</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39690753270857</v>
+        <v>11.67725414937293</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13675120065075</v>
+        <v>59.94323796678104</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576106768553949</v>
+        <v>0.7784836099581953</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.009277697694727</v>
+        <v>2.464186737659494</v>
       </c>
       <c r="C2" t="n">
-        <v>7.469136533909733</v>
+        <v>7.413176914767665</v>
       </c>
       <c r="D2" t="n">
-        <v>24.88239556413541</v>
+        <v>16.79770321966293</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.39857387239098</v>
+        <v>12.91489104936679</v>
       </c>
       <c r="C3" t="n">
-        <v>19.55150553007523</v>
+        <v>26.40410450571797</v>
       </c>
       <c r="D3" t="n">
-        <v>32.95236169304419</v>
+        <v>31.55337121449249</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.58626761035137</v>
+        <v>6.011241193103221</v>
       </c>
       <c r="C4" t="n">
-        <v>25.5764911910379</v>
+        <v>32.00890214926301</v>
       </c>
       <c r="D4" t="n">
-        <v>23.21538796232432</v>
+        <v>22.32199755145973</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4363194148629</v>
+        <v>13.62660677481972</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11841357765616</v>
+        <v>73.7439896049067</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24975145576061</v>
+        <v>1.60313020880232</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.615016031215008</v>
+        <v>1.59730351480956</v>
       </c>
       <c r="C2" t="n">
-        <v>6.332272692391927</v>
+        <v>7.474045272430967</v>
       </c>
       <c r="D2" t="n">
-        <v>27.61165418194154</v>
+        <v>23.78676512619597</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.51009220004762</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C3" t="n">
-        <v>25.21128104505809</v>
+        <v>28.01417074068273</v>
       </c>
       <c r="D3" t="n">
-        <v>45.20948178056562</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.60424216866407</v>
+        <v>17.43387573201486</v>
       </c>
       <c r="C4" t="n">
-        <v>38.84972015245478</v>
+        <v>53.14396672628834</v>
       </c>
       <c r="D4" t="n">
-        <v>34.49763257952867</v>
+        <v>33.68081848959532</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.37693436516855</v>
+        <v>6.086835766330226</v>
       </c>
       <c r="C5" t="n">
-        <v>29.28062527916113</v>
+        <v>37.52730599483434</v>
       </c>
       <c r="D5" t="n">
-        <v>30.99868376159304</v>
+        <v>27.9798095710341</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72433288515925</v>
+        <v>14.83558215100657</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0184305994714</v>
+        <v>87.36509488926093</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181083221289812</v>
+        <v>2.472597025167762</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.516841260790327</v>
+        <v>1.517781950765569</v>
       </c>
       <c r="C2" t="n">
-        <v>4.985314842165304</v>
+        <v>6.941938016729196</v>
       </c>
       <c r="D2" t="n">
-        <v>30.43319708394688</v>
+        <v>22.00391129528376</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.06477965294707</v>
+        <v>7.647814616082653</v>
       </c>
       <c r="C3" t="n">
-        <v>24.81858196335937</v>
+        <v>28.66212422548563</v>
       </c>
       <c r="D3" t="n">
-        <v>56.13633372883262</v>
+        <v>48.23817344816703</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.66278717802039</v>
+        <v>19.01645303126072</v>
       </c>
       <c r="C4" t="n">
-        <v>51.76559294952582</v>
+        <v>63.18822748843746</v>
       </c>
       <c r="D4" t="n">
-        <v>48.58767563087889</v>
+        <v>45.16726662928301</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.91938318172731</v>
+        <v>16.73879835740812</v>
       </c>
       <c r="C5" t="n">
-        <v>52.20443417332415</v>
+        <v>72.1339125695344</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85833489761475</v>
+        <v>33.55122779263475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.49059611468292</v>
+        <v>6.520768251607316</v>
       </c>
       <c r="C6" t="n">
-        <v>29.98748362621883</v>
+        <v>37.35353665118265</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04168963094358</v>
+        <v>16.07531190725393</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7005466399652</v>
+        <v>101.5282857300248</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013896543647858</v>
+        <v>3.384276191000829</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.441246687563323</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C2" t="n">
-        <v>6.313619486011237</v>
+        <v>12.28362727553609</v>
       </c>
       <c r="D2" t="n">
-        <v>33.95767134219292</v>
+        <v>18.50790772046087</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65949777754238</v>
+        <v>6.302820261264523</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39089981720625</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D3" t="n">
-        <v>62.82694433327463</v>
+        <v>54.2317431825938</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.09900195387546</v>
+        <v>16.87231604518568</v>
       </c>
       <c r="C4" t="n">
-        <v>48.0005905037393</v>
+        <v>67.96148482648545</v>
       </c>
       <c r="D4" t="n">
-        <v>56.60266388834985</v>
+        <v>58.42773287054467</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.56256679672921</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="C5" t="n">
-        <v>55.32148313430778</v>
+        <v>96.21127501618744</v>
       </c>
       <c r="D5" t="n">
-        <v>35.93196597543326</v>
+        <v>41.40520942660923</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.50317890838889</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>38.68184129502858</v>
+        <v>76.96116603131597</v>
       </c>
       <c r="D6" t="n">
-        <v>31.91956310817655</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>20.54110721595601</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.047725173015727</v>
+        <v>17.34035903018714</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07242349702244</v>
+        <v>114.4463695992351</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404828233134829</v>
+        <v>4.335089757546784</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.058365082907066</v>
+        <v>2.581014714464864</v>
       </c>
       <c r="C2" t="n">
-        <v>10.64214511403543</v>
+        <v>13.77588378599124</v>
       </c>
       <c r="D2" t="n">
-        <v>29.57024085191393</v>
+        <v>22.07165188687679</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4364611222291</v>
+        <v>7.01458734684346</v>
       </c>
       <c r="C3" t="n">
-        <v>23.09561474240621</v>
+        <v>38.78394305627025</v>
       </c>
       <c r="D3" t="n">
-        <v>76.16889563398878</v>
+        <v>56.01361526580177</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.03366682604742</v>
+        <v>14.47292465600648</v>
       </c>
       <c r="C4" t="n">
-        <v>49.97881212779662</v>
+        <v>67.85938306524379</v>
       </c>
       <c r="D4" t="n">
-        <v>76.39764284907828</v>
+        <v>70.90967318233861</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.81553890925539</v>
+        <v>24.05281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>74.93189352663781</v>
+        <v>111.0847527355266</v>
       </c>
       <c r="D5" t="n">
-        <v>48.47379289718628</v>
+        <v>51.32086123950202</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.53842401475054</v>
+        <v>22.25916569838794</v>
       </c>
       <c r="C6" t="n">
-        <v>67.66303352439442</v>
+        <v>114.1939477148763</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>41.66046382971341</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.89369351050086</v>
+        <v>11.79766216193392</v>
       </c>
       <c r="C7" t="n">
-        <v>41.20198765183014</v>
+        <v>72.10347839070273</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>23.94973524510094</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.265855849725813</v>
+        <v>17.73723103575615</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3832544409053</v>
+        <v>126.8212019056564</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449391887294359</v>
+        <v>5.321169310726844</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.912084674974292</v>
+        <v>2.291399141712055</v>
       </c>
       <c r="C2" t="n">
-        <v>7.121597846606362</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="D2" t="n">
-        <v>39.7980884347572</v>
+        <v>17.34257319551991</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.12721059539136</v>
+        <v>9.58185759344887</v>
       </c>
       <c r="C3" t="n">
-        <v>33.99792299806705</v>
+        <v>58.12437282993241</v>
       </c>
       <c r="D3" t="n">
-        <v>82.15264789137309</v>
+        <v>62.93493658074178</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.60722846950582</v>
+        <v>11.55026174046372</v>
       </c>
       <c r="C4" t="n">
-        <v>54.53510322320607</v>
+        <v>97.78796182920779</v>
       </c>
       <c r="D4" t="n">
-        <v>97.41784294470675</v>
+        <v>66.00878864273855</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.67581194008286</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>84.74937056910592</v>
+        <v>68.23146544515333</v>
       </c>
       <c r="D5" t="n">
-        <v>64.94261063592651</v>
+        <v>40.15348110369455</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.84913931537804</v>
+        <v>7.3258013690897</v>
       </c>
       <c r="C6" t="n">
-        <v>94.83290123942491</v>
+        <v>47.45670227558657</v>
       </c>
       <c r="D6" t="n">
-        <v>43.14977509705582</v>
+        <v>26.08307300642926</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>72.04359178074368</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>26.76931465169778</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>40.63944621729671</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
         <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.470783268994486</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.04631177618796</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.536935360370175</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
